--- a/demo_data/sectors/insaat_taahhut/inventory.xlsx
+++ b/demo_data/sectors/insaat_taahhut/inventory.xlsx
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>96.73999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="D2" t="n">
         <v>24500</v>
       </c>
       <c r="E2" t="n">
-        <v>2370130</v>
+        <v>2370290.09</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>46002</v>
